--- a/docs/dominio-metrico/migracion/cuestionarios/cegar-para-ver-mejor.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/cegar-para-ver-mejor.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · Cegar para ver mejor</t>
   </si>
   <si>
-    <t>Para Gabriel López · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para Gabriel López · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/cegar-para-ver-mejor.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/cegar-para-ver-mejor.xlsx
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -168,7 +168,7 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
+    <t>Sílabas del verso</t>
   </si>
   <si>
     <t>#</t>
@@ -956,7 +956,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>

--- a/docs/dominio-metrico/migracion/cuestionarios/cegar-para-ver-mejor.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/cegar-para-ver-mejor.xlsx
@@ -21,7 +21,7 @@
     <t>Migración métrica · Cegar para ver mejor</t>
   </si>
   <si>
-    <t>Para Gabriel López · generado el 2026-09-20</t>
+    <t>Para Gabriel López · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/cegar-para-ver-mejor.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/cegar-para-ver-mejor.xlsx
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/cegar-para-ver-mejor.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/cegar-para-ver-mejor.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="63">
   <si>
     <t>Migración métrica · Cegar para ver mejor</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» dice el formato y da un ejemplo.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -40,21 +40,6 @@
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
-  </si>
-  <si>
-    <t>Cuando no hay desplegable, los formatos son estos:</t>
-  </si>
-  <si>
-    <t>Medidas: el número de sílabas de cada verso, en orden y separados por espacios. Por ejemplo, «7 11 7 7 11 7 11 11».</t>
-  </si>
-  <si>
-    <t>Posiciones: en qué versos de la estrofa cae el quebrado y cuántas sílabas tiene cada uno, separados por comas. Por ejemplo, «3: 4, 8: 5» quiere decir que el verso 3 tiene cuatro sílabas y el 8 tiene cinco.</t>
-  </si>
-  <si>
-    <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
-  </si>
-  <si>
-    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -284,14 +269,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -640,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -684,31 +668,6 @@
     <row r="9" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -727,17 +686,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -762,36 +721,36 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -817,120 +776,120 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>25</v>
+      <c r="H1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -962,36 +921,36 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>25</v>
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1019,39 +978,39 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1059,34 +1018,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3">
         <v>244</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1094,34 +1053,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3">
         <v>176</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="K3" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1129,34 +1088,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3">
         <v>64</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
